--- a/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsReconDetail.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsReconDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26940" windowHeight="4485"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -83,7 +83,7 @@
     <t>{.supplierName}</t>
   </si>
   <si>
-    <t>{.fileName}</t>
+    <t>{.sheetName}</t>
   </si>
   <si>
     <t>{.soCode}</t>
